--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -168,7 +168,7 @@
     <col min="12" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="48" customWidth="1"/>
     <col min="14" max="14" width="48" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="36" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
@@ -284,7 +284,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betrag beantragen (€)</t>
+          <t xml:space="preserve">Erwartete Summe (€)</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -816,7 +816,7 @@
       <formula1>"Portal,E-Mail,Brief,Persönlich,Telefon,Sonstiges"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="O11:O310">
-      <formula1>"klappt wahrscheinlich,unsicher,eher nicht"</formula1>
+      <formula1>"sehr wahrscheinlich,wahrscheinlich,unsicher,unwahrscheinlich,sehr unwahrscheinlich"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -1027,12 +1027,12 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betrag beantragen (€)</t>
+          <t xml:space="preserve">Erwartete Summe (€)</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorschlag, wie viel bei diesem Förderer beantragt wird – nur die Zahl in Euro.</t>
+          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nur: klappt wahrscheinlich · unsicher · eher nicht. Auswahl: klappt wahrscheinlich · unsicher · eher nicht</t>
+          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
         </is>
       </c>
     </row>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -299,12 +299,12 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warum passt das?</t>
+          <t xml:space="preserve">Pro – warum passt das?</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knackpunkte</t>
+          <t xml:space="preserve">Contra – Knackpunkte</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warum passt das?</t>
+          <t xml:space="preserve">Pro – warum passt das?</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knackpunkte</t>
+          <t xml:space="preserve">Contra – Knackpunkte</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -155,22 +155,23 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="48" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="14" width="48" customWidth="1"/>
-    <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="16" width="36" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="15" max="15" width="48" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="36" customWidth="1"/>
+    <col min="18" max="18" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -183,7 +184,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je möglichem Förderer eine Zeile ausfüllen. Spaltenüberschriften und Blattnamen nicht ändern. Was in jede Spalte gehört, steht im Blatt „Anleitung“. Danach in der Bedarfsliste „Aus Excel übernehmen“ wählen.</t>
+          <t xml:space="preserve">Je möglichem Förderer eine Zeile ausfüllen. Spaltenüberschriften und Blattnamen nicht ändern. Auftrag, Umfang und was in jede Spalte gehört, stehen im Blatt „Anleitung“. Danach in der Bedarfsliste „Excel übernehmen“ wählen.</t>
         </is>
       </c>
     </row>
@@ -215,15 +216,15 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deadline</t>
+          <t xml:space="preserve">Eigenmittel (€)</t>
         </is>
       </c>
       <c r="B7" s="4"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beschreibung</t>
+          <t xml:space="preserve">Schon zugesagt (€)</t>
         </is>
       </c>
       <c r="B8" s="4"/>
@@ -231,192 +232,135 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Noch offen (€)</t>
+        </is>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deadline</t>
+        </is>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stichwort oder Fördertopf</t>
+        </is>
+      </c>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beschreibung</t>
+        </is>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kennung</t>
         </is>
       </c>
-      <c r="B9" s="5"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Förderer</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stand in der Bedarfsliste</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Art</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Antragsweg</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ansprechperson oder Portal</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">E-Mail</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Telefon</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Website oder Portal-Link</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Antragsfrist</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Weitere Fristen und Termine</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Erwartete Summe (€)</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Übliche Fördersumme</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Eigenanteil gefordert</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Pro – warum passt das?</t>
         </is>
       </c>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Contra – Knackpunkte</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Einschätzung</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Quellen</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Notizen</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
     </row>
     <row r="16">
       <c r="A16" s="7"/>
@@ -426,16 +370,17 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="9"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="10"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="7"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
     </row>
     <row r="17">
       <c r="A17" s="7"/>
@@ -445,16 +390,17 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="9"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="7"/>
       <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
     </row>
     <row r="18">
       <c r="A18" s="7"/>
@@ -464,16 +410,17 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="9"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="10"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="7"/>
       <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
     </row>
     <row r="19">
       <c r="A19" s="7"/>
@@ -483,16 +430,17 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="9"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="7"/>
       <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="7"/>
@@ -502,16 +450,17 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="9"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="10"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="7"/>
       <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="7"/>
@@ -521,16 +470,17 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="9"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="10"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="7"/>
       <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
     </row>
     <row r="22">
       <c r="A22" s="7"/>
@@ -540,16 +490,17 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="9"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="10"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="7"/>
       <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
     </row>
     <row r="23">
       <c r="A23" s="7"/>
@@ -559,16 +510,17 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="9"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="10"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="7"/>
       <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
     </row>
     <row r="24">
       <c r="A24" s="7"/>
@@ -578,16 +530,17 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="9"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="10"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="7"/>
       <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
     </row>
     <row r="25">
       <c r="A25" s="7"/>
@@ -597,16 +550,17 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="9"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="10"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="7"/>
       <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
     </row>
     <row r="26">
       <c r="A26" s="7"/>
@@ -616,16 +570,17 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="9"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="10"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="7"/>
       <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
     </row>
     <row r="27">
       <c r="A27" s="7"/>
@@ -635,16 +590,17 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="9"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="10"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="7"/>
       <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
     </row>
     <row r="28">
       <c r="A28" s="7"/>
@@ -654,16 +610,17 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="9"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="10"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="7"/>
       <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
     </row>
     <row r="29">
       <c r="A29" s="7"/>
@@ -673,16 +630,17 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="9"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="10"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="7"/>
       <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
     </row>
     <row r="30">
       <c r="A30" s="7"/>
@@ -692,16 +650,17 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="9"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="10"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="7"/>
       <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
     </row>
     <row r="31">
       <c r="A31" s="7"/>
@@ -711,16 +670,17 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="9"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="10"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="7"/>
       <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
     </row>
     <row r="32">
       <c r="A32" s="7"/>
@@ -730,16 +690,17 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="9"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="10"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="7"/>
       <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
     </row>
     <row r="33">
       <c r="A33" s="7"/>
@@ -749,16 +710,17 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="9"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="10"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="7"/>
       <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
     </row>
     <row r="34">
       <c r="A34" s="7"/>
@@ -768,16 +730,17 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="9"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="10"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="7"/>
       <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
     </row>
     <row r="35">
       <c r="A35" s="7"/>
@@ -787,35 +750,140 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="9"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="10"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="7"/>
       <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:I12"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="B11:B310">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="C16:C315">
       <formula1>"Stiftung,Sparkasse,Volksbank / Bank,Unternehmen,Soziallotterie,Öffentliche Förderung,Kirchliche Stelle,Sonstiges"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="C11:C310">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="D16:D315">
       <formula1>"Portal,E-Mail,Brief,Persönlich,Telefon,Sonstiges"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="O11:O310">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="P16:P315">
       <formula1>"sehr wahrscheinlich,wahrscheinlich,unsicher,unwahrscheinlich,sehr unwahrscheinlich"</formula1>
     </dataValidation>
   </dataValidations>
@@ -839,299 +907,345 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="49" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diese Datei ist die Vorlage für den Förderplan eines Bedarfs aus der Bedarfsliste (Fundraising, Malteser Hilfsdienst e. V., Diözese Paderborn). Sie wird von Hand oder von einer KI ausgefüllt und danach in der Bedarfsliste über „Aus Excel übernehmen“ eingelesen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auftrag: Finde Förderer, die zum Bedarf oben im Blatt „Förderplan“ passen – Stiftungen, Sparkassen und Volksbanken, Unternehmen, Soziallotterien, öffentliche und kirchliche Förderprogramme. Förderer mit Bezug zur Region der Gliederung zuerst. Prüfe Satzungszweck, Förderrichtlinien, Fristen und Förderhöhe auf den Seiten der Förderer und nenne die Quellen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regeln</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t xml:space="preserve">Diese Datei ist die Vorlage für den Förderplan eines Bedarfs aus der Bedarfsliste (Fundraising, Malteser Hilfsdienst e. V., Diözese Paderborn). Sie wird von Hand oder von Copilot ausgefüllt und danach in der Bedarfsliste über „Excel übernehmen“ eingelesen. Der Bedarf mit Summe und noch offenem Betrag steht oben im Blatt „Förderplan“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auftrag</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Finde Förderer, die zu diesem Bedarf passen: Stiftungen, Sparkassen und Volksbanken, Unternehmen, Soziallotterien sowie öffentliche und kirchliche Förderprogramme. Förderer mit Bezug zum Erzbistum Paderborn und zu NRW zuerst, danach bundesweit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Je Förderer genau eine Zeile im Blatt „Förderplan“, ab der Zeile unter den Überschriften.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t xml:space="preserve">2. Prüfe jeden Förderer auf seinen eigenen Seiten: Satzungszweck, Förderrichtlinien, Antragsfristen, übliche Förderhöhe, geforderter Eigenanteil und Antragsweg. Nenne die Links als Quellen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Spaltenüberschriften, Blattnamen und die Angaben oben (Bedarf, Kennung) nicht ändern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Schon eingetragene Förderer ergänzen, nicht löschen oder doppelt anlegen.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">3. Förderer, die im Blatt „Förderplan“ schon stehen, nicht doppelt anlegen. Steht dort „zugesagt“ oder „abgelehnt“, die Zeile nicht ändern; sonst nur leere Zellen ergänzen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Datum immer als TT.MM.JJJJ, Beträge nur als Zahl in Euro (ohne Text).</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umfang</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">8 bis 12 Förderer, sortiert nach Erfolgsaussicht. Lieber weniger Förderer mit Beleg als viele unsichere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regeln</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Je Förderer genau eine Zeile im Blatt „Förderplan“, ab der Zeile unter den Überschriften.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Spaltenüberschriften, Blattnamen und die Angaben oben (Bedarf, Kennung) nicht ändern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Datum immer als TT.MM.JJJJ, Beträge nur als Zahl in Euro (ohne Text).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">• Art, Antragsweg und Einschätzung aus der Auswahlliste der Zelle wählen.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">• Unsicheres als solches kennzeichnen (z. B. „laut Website 2025, nicht bestätigt“). Nichts erfinden: lieber eine Zelle leer lassen.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Spalte</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Was gehört hinein</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Förderer</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name der Stiftung, Bank, Firma oder des Förderprogramms – genau so, wie er in der Förder-Kartei steht, falls er dort schon vorkommt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Art</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aus der Auswahlliste. Auswahl: Stiftung · Sparkasse · Volksbank / Bank · Unternehmen · Soziallotterie · Öffentliche Förderung · Kirchliche Stelle · Sonstiges</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Antragsweg</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wie der Antrag gestellt wird – aus der Auswahlliste. Auswahl: Portal · E-Mail · Brief · Persönlich · Telefon · Sonstiges</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ansprechperson oder Portal</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name und Funktion der zuständigen Person oder Name des Antragsportals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E-Mail</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E-Mail-Adresse der Ansprechperson oder der Förderstelle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telefon</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telefonnummer.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website oder Portal-Link</t>
+          <t xml:space="preserve">Förderer</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link zur Förderseite oder zum Antragsportal.</t>
+          <t xml:space="preserve">Name der Stiftung, Bank, Firma oder des Förderprogramms – genau so, wie er in der Förder-Kartei steht, falls er dort schon vorkommt.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antragsfrist</t>
+          <t xml:space="preserve">Stand in der Bedarfsliste</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nächster Einsendeschluss als Datum (TT.MM.JJJJ). Laufende Antragstellung: leer lassen und unter „Weitere Fristen und Termine“ notieren.</t>
+          <t xml:space="preserve">Nur zur Information: wie weit der Förderer schon ist. Wird nicht eingelesen. Bei neuen Förderern leer lassen.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weitere Fristen und Termine</t>
+          <t xml:space="preserve">Art</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vergabesitzungen, Stichtage, Bearbeitungszeit, „laufend“ usw.</t>
+          <t xml:space="preserve">Aus der Auswahlliste. Auswahl: Stiftung · Sparkasse · Volksbank / Bank · Unternehmen · Soziallotterie · Öffentliche Förderung · Kirchliche Stelle · Sonstiges</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erwartete Summe (€)</t>
+          <t xml:space="preserve">Antragsweg</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
+          <t xml:space="preserve">Wie der Antrag gestellt wird – aus der Auswahlliste. Auswahl: Portal · E-Mail · Brief · Persönlich · Telefon · Sonstiges</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Übliche Fördersumme</t>
+          <t xml:space="preserve">Ansprechperson oder Portal</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typische oder maximale Förderhöhe laut Richtlinien oder Förderhistorie.</t>
+          <t xml:space="preserve">Name und Funktion der zuständigen Person oder Name des Antragsportals.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eigenanteil gefordert</t>
+          <t xml:space="preserve">E-Mail</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ob und wie viel Eigenanteil verlangt wird.</t>
+          <t xml:space="preserve">E-Mail-Adresse der Ansprechperson oder der Förderstelle.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pro – warum passt das?</t>
+          <t xml:space="preserve">Telefon</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Begründung: Satzungszweck, Förderschwerpunkt, Regionalbezug, frühere Förderungen.</t>
+          <t xml:space="preserve">Telefonnummer.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contra – Knackpunkte</t>
+          <t xml:space="preserve">Website oder Portal-Link</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wo es haken kann und worauf der Antrag den Fokus legen sollte.</t>
+          <t xml:space="preserve">Link zur Förderseite oder zum Antragsportal.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Einschätzung</t>
+          <t xml:space="preserve">Antragsfrist</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
+          <t xml:space="preserve">Nächster Einsendeschluss als Datum (TT.MM.JJJJ). Laufende Antragstellung: leer lassen und unter „Weitere Fristen und Termine“ notieren.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quellen</t>
+          <t xml:space="preserve">Weitere Fristen und Termine</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Links zu Satzung, Förderrichtlinien und weiteren Belegen.</t>
+          <t xml:space="preserve">Vergabesitzungen, Stichtage, Bearbeitungszeit, „laufend“ usw.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Erwartete Summe (€)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Übliche Fördersumme</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Typische oder maximale Förderhöhe laut Richtlinien oder Förderhistorie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eigenanteil gefordert</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ob und wie viel Eigenanteil verlangt wird.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pro – warum passt das?</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Begründung: Satzungszweck, Förderschwerpunkt, Regionalbezug, frühere Förderungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contra – Knackpunkte</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wo es haken kann und worauf der Antrag den Fokus legen sollte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Einschätzung</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quellen</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Links zu Satzung, Förderrichtlinien und weiteren Belegen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Notizen</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Alles Weitere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Prüfe jeden Förderer auf seinen eigenen Seiten: Satzungszweck, Förderrichtlinien, Antragsfristen, übliche Förderhöhe, geforderter Eigenanteil und Antragsweg. Nenne die Links als Quellen.</t>
+          <t xml:space="preserve">2. Recherchiere im Web und prüfe jeden Förderer auf seinen eigenen Seiten: Satzungszweck, Förderrichtlinien, Antragsfristen, übliche Förderhöhe, geforderter Eigenanteil und Antragsweg. Trage als Quellen nur Links ein, die du dabei tatsächlich geöffnet hast. Wenn du nicht im Web suchen kannst, brich ab und sag es mir.</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="49" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 bis 12 Förderer, sortiert nach Erfolgsaussicht. Lieber weniger Förderer mit Beleg als viele unsichere.</t>
+          <t xml:space="preserve">5 bis 8 Förderer, sortiert nach Erfolgsaussicht. Die erwartete Summe je Förderer realistisch aus Förderhistorie, Richtlinien oder üblicher Förderhöhe ableiten; geht das nicht, die Zelle leer lassen. Nicht auf eine Gesamtsumme hinrechnen. Lieber weniger Förderer mit Beleg als viele unsichere.</t>
         </is>
       </c>
     </row>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -997,241 +997,255 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">• Kurze Felder kurz halten: „Ansprechperson oder Portal“, „Übliche Fördersumme“ und „Eigenanteil gefordert“ höchstens etwa 80 Zeichen – Erläuterungen gehören in „Notizen“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Quellen: je Link eine eigene Zeile in der Zelle, nur die Adresse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">• Unsicheres als solches kennzeichnen (z. B. „laut Website 2025, nicht bestätigt“). Nichts erfinden: lieber eine Zelle leer lassen.</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Spalte</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Was gehört hinein</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Förderer</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name der Stiftung, Bank, Firma oder des Förderprogramms – genau so, wie er in der Förder-Kartei steht, falls er dort schon vorkommt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stand in der Bedarfsliste</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nur zur Information: wie weit der Förderer schon ist. Wird nicht eingelesen. Bei neuen Förderern leer lassen.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Art</t>
+          <t xml:space="preserve">Förderer</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aus der Auswahlliste. Auswahl: Stiftung · Sparkasse · Volksbank / Bank · Unternehmen · Soziallotterie · Öffentliche Förderung · Kirchliche Stelle · Sonstiges</t>
+          <t xml:space="preserve">Name der Stiftung, Bank, Firma oder des Förderprogramms – genau so, wie er in der Förder-Kartei steht, falls er dort schon vorkommt.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antragsweg</t>
+          <t xml:space="preserve">Stand in der Bedarfsliste</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wie der Antrag gestellt wird – aus der Auswahlliste. Auswahl: Portal · E-Mail · Brief · Persönlich · Telefon · Sonstiges</t>
+          <t xml:space="preserve">Nur zur Information: wie weit der Förderer schon ist. Wird nicht eingelesen. Bei neuen Förderern leer lassen.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ansprechperson oder Portal</t>
+          <t xml:space="preserve">Art</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name und Funktion der zuständigen Person oder Name des Antragsportals.</t>
+          <t xml:space="preserve">Aus der Auswahlliste. Auswahl: Stiftung · Sparkasse · Volksbank / Bank · Unternehmen · Soziallotterie · Öffentliche Förderung · Kirchliche Stelle · Sonstiges</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-Mail</t>
+          <t xml:space="preserve">Antragsweg</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-Mail-Adresse der Ansprechperson oder der Förderstelle.</t>
+          <t xml:space="preserve">Wie der Antrag gestellt wird – aus der Auswahlliste. Auswahl: Portal · E-Mail · Brief · Persönlich · Telefon · Sonstiges</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefon</t>
+          <t xml:space="preserve">Ansprechperson oder Portal</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefonnummer.</t>
+          <t xml:space="preserve">Name und Funktion der zuständigen Person oder Name des Antragsportals – kurz, höchstens etwa 80 Zeichen.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website oder Portal-Link</t>
+          <t xml:space="preserve">E-Mail</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link zur Förderseite oder zum Antragsportal.</t>
+          <t xml:space="preserve">E-Mail-Adresse der Ansprechperson oder der Förderstelle.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antragsfrist</t>
+          <t xml:space="preserve">Telefon</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nächster Einsendeschluss als Datum (TT.MM.JJJJ). Laufende Antragstellung: leer lassen und unter „Weitere Fristen und Termine“ notieren.</t>
+          <t xml:space="preserve">Telefonnummer.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weitere Fristen und Termine</t>
+          <t xml:space="preserve">Website oder Portal-Link</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vergabesitzungen, Stichtage, Bearbeitungszeit, „laufend“ usw.</t>
+          <t xml:space="preserve">Link zur Förderseite oder zum Antragsportal.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erwartete Summe (€)</t>
+          <t xml:space="preserve">Antragsfrist</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
+          <t xml:space="preserve">Nächster Einsendeschluss als Datum (TT.MM.JJJJ). Laufende Antragstellung: leer lassen und unter „Weitere Fristen und Termine“ notieren.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Übliche Fördersumme</t>
+          <t xml:space="preserve">Weitere Fristen und Termine</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typische oder maximale Förderhöhe laut Richtlinien oder Förderhistorie.</t>
+          <t xml:space="preserve">Vergabesitzungen, Stichtage, Bearbeitungszeit, „laufend“ usw.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eigenanteil gefordert</t>
+          <t xml:space="preserve">Erwartete Summe (€)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ob und wie viel Eigenanteil verlangt wird.</t>
+          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pro – warum passt das?</t>
+          <t xml:space="preserve">Übliche Fördersumme</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Begründung: Satzungszweck, Förderschwerpunkt, Regionalbezug, frühere Förderungen.</t>
+          <t xml:space="preserve">Typische oder maximale Förderhöhe laut Richtlinien oder Förderhistorie – kurz, z. B. „1.000–5.000 €, max. 10.000 €“ (höchstens etwa 80 Zeichen; Erläuterungen in „Notizen“).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contra – Knackpunkte</t>
+          <t xml:space="preserve">Eigenanteil gefordert</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wo es haken kann und worauf der Antrag den Fokus legen sollte.</t>
+          <t xml:space="preserve">Ob und wie viel Eigenanteil verlangt wird – kurz, z. B. „ja, mind. 20 %“ oder „nein“ (höchstens etwa 80 Zeichen; Erläuterungen in „Notizen“).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Einschätzung</t>
+          <t xml:space="preserve">Pro – warum passt das?</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
+          <t xml:space="preserve">Begründung: Satzungszweck, Förderschwerpunkt, Regionalbezug, frühere Förderungen.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quellen</t>
+          <t xml:space="preserve">Contra – Knackpunkte</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Links zu Satzung, Förderrichtlinien und weiteren Belegen.</t>
+          <t xml:space="preserve">Wo es haken kann und worauf der Antrag den Fokus legen sollte.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Einschätzung</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quellen</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Links zu Satzung, Förderrichtlinien und weiteren Belegen – je Link eine eigene Zeile in der Zelle (Zeilenumbruch), nur die Adresse, keine Trennzeichen wie „;“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Notizen</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Alles Weitere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -1246,6 +1260,8 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -127,11 +127,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -158,7 +158,7 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
@@ -293,7 +293,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ansprechperson oder Portal</t>
+          <t xml:space="preserve">Kontakte</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -367,500 +367,500 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="8"/>
       <c r="K16" s="10"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
       <c r="P16" s="7"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
     </row>
     <row r="17">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="8"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="7"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
     </row>
     <row r="18">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="8"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
       <c r="P18" s="7"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
     </row>
     <row r="19">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="8"/>
       <c r="K19" s="10"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
       <c r="P19" s="7"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
     </row>
     <row r="20">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="8"/>
       <c r="K20" s="10"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
       <c r="P20" s="7"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
     </row>
     <row r="21">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="8"/>
       <c r="K21" s="10"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
       <c r="P21" s="7"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="9"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
     </row>
     <row r="22">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="8"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
       <c r="P22" s="7"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
     </row>
     <row r="23">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="8"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
       <c r="P23" s="7"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
     </row>
     <row r="24">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="8"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
       <c r="P24" s="7"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
     </row>
     <row r="25">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="8"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
       <c r="P25" s="7"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="8"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
       <c r="P26" s="7"/>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="9"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
     </row>
     <row r="27">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="E27" s="8"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="8"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
       <c r="P27" s="7"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
     </row>
     <row r="28">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="E28" s="8"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="8"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
       <c r="P28" s="7"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
     </row>
     <row r="29">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="8"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="8"/>
       <c r="K29" s="10"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
       <c r="P29" s="7"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
     </row>
     <row r="30">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="8"/>
       <c r="K30" s="10"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
       <c r="P30" s="7"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="9"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
     </row>
     <row r="31">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="8"/>
       <c r="K31" s="10"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
       <c r="P31" s="7"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
     </row>
     <row r="32">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="E32" s="8"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="8"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
       <c r="P32" s="7"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
     </row>
     <row r="33">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="8"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="8"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
       <c r="P33" s="7"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
     </row>
     <row r="34">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="8"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
       <c r="P34" s="7"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
     </row>
     <row r="35">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="8"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
       <c r="P35" s="7"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8"/>
     </row>
     <row r="36">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="8"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
       <c r="P36" s="7"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8"/>
     </row>
     <row r="37">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="8"/>
       <c r="K37" s="10"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
       <c r="P37" s="7"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
+      <c r="Q37" s="8"/>
+      <c r="R37" s="8"/>
     </row>
     <row r="38">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="E38" s="8"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="8"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
       <c r="P38" s="7"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="8"/>
     </row>
     <row r="39">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="E39" s="8"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="8"/>
       <c r="K39" s="10"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
       <c r="P39" s="7"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
     </row>
     <row r="40">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="8"/>
       <c r="K40" s="10"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
       <c r="P40" s="7"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -994,258 +994,265 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="34" customHeight="1">
+    <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Kurze Felder kurz halten: „Ansprechperson oder Portal“, „Übliche Fördersumme“ und „Eigenanteil gefordert“ höchstens etwa 80 Zeichen – Erläuterungen gehören in „Notizen“.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t xml:space="preserve">• Kontakte: bis zu drei Personen, je Person eine Zeile in der Zelle „Name; Funktion; E-Mail; Telefon“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">• Kurze Felder kurz halten: „Übliche Fördersumme“ und „Eigenanteil gefordert“ höchstens etwa 80 Zeichen – Erläuterungen gehören in „Notizen“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">• Quellen: je Link eine eigene Zeile in der Zelle, nur die Adresse.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">• Unsicheres als solches kennzeichnen (z. B. „laut Website 2025, nicht bestätigt“). Nichts erfinden: lieber eine Zelle leer lassen.</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Spalte</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Was gehört hinein</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Förderer</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name der Stiftung, Bank, Firma oder des Förderprogramms – genau so, wie er in der Förder-Kartei steht, falls er dort schon vorkommt.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stand in der Bedarfsliste</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nur zur Information: wie weit der Förderer schon ist. Wird nicht eingelesen. Bei neuen Förderern leer lassen.</t>
+          <t xml:space="preserve">Förderer</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name der Stiftung, Bank, Firma oder des Förderprogramms – genau so, wie er in der Förder-Kartei steht, falls er dort schon vorkommt.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Art</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aus der Auswahlliste. Auswahl: Stiftung · Sparkasse · Volksbank / Bank · Unternehmen · Soziallotterie · Öffentliche Förderung · Kirchliche Stelle · Sonstiges</t>
+          <t xml:space="preserve">Stand in der Bedarfsliste</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nur zur Information: wie weit der Förderer schon ist. Wird nicht eingelesen. Bei neuen Förderern leer lassen.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antragsweg</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wie der Antrag gestellt wird – aus der Auswahlliste. Auswahl: Portal · E-Mail · Brief · Persönlich · Telefon · Sonstiges</t>
+          <t xml:space="preserve">Art</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aus der Auswahlliste. Auswahl: Stiftung · Sparkasse · Volksbank / Bank · Unternehmen · Soziallotterie · Öffentliche Förderung · Kirchliche Stelle · Sonstiges</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ansprechperson oder Portal</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name und Funktion der zuständigen Person oder Name des Antragsportals – kurz, höchstens etwa 80 Zeichen.</t>
+          <t xml:space="preserve">Antragsweg</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie der Antrag gestellt wird – aus der Auswahlliste. Auswahl: Portal · E-Mail · Brief · Persönlich · Telefon · Sonstiges</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-Mail</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E-Mail-Adresse der Ansprechperson oder der Förderstelle.</t>
+          <t xml:space="preserve">Kontakte</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bis zu drei Ansprechpersonen, je Person eine Zeile in der Zelle: Name; Funktion; E-Mail; Telefon (Unbekanntes weglassen). Wichtigste Person zuerst. Bei Antrag nur über ein Portal: Name des Portals.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefon</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telefonnummer.</t>
+          <t xml:space="preserve">E-Mail</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allgemeine E-Mail-Adresse der Förderstelle (gilt für die erste Person, wenn sie keine eigene hat).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website oder Portal-Link</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link zur Förderseite oder zum Antragsportal.</t>
+          <t xml:space="preserve">Telefon</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allgemeine Telefonnummer der Förderstelle (gilt für die erste Person, wenn sie keine eigene hat).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antragsfrist</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nächster Einsendeschluss als Datum (TT.MM.JJJJ). Laufende Antragstellung: leer lassen und unter „Weitere Fristen und Termine“ notieren.</t>
+          <t xml:space="preserve">Website oder Portal-Link</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Link zur Förderseite oder zum Antragsportal.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weitere Fristen und Termine</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vergabesitzungen, Stichtage, Bearbeitungszeit, „laufend“ usw.</t>
+          <t xml:space="preserve">Antragsfrist</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nächster Einsendeschluss als Datum (TT.MM.JJJJ). Laufende Antragstellung: leer lassen und unter „Weitere Fristen und Termine“ notieren.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erwartete Summe (€)</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
+          <t xml:space="preserve">Weitere Fristen und Termine</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vergabesitzungen, Stichtage, Bearbeitungszeit, „laufend“ usw.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Übliche Fördersumme</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Typische oder maximale Förderhöhe laut Richtlinien oder Förderhistorie – kurz, z. B. „1.000–5.000 €, max. 10.000 €“ (höchstens etwa 80 Zeichen; Erläuterungen in „Notizen“).</t>
+          <t xml:space="preserve">Erwartete Summe (€)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie viel von diesem Förderer zu erwarten ist bzw. beantragt werden sollte – eine feste Summe, nur die Zahl in Euro.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eigenanteil gefordert</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ob und wie viel Eigenanteil verlangt wird – kurz, z. B. „ja, mind. 20 %“ oder „nein“ (höchstens etwa 80 Zeichen; Erläuterungen in „Notizen“).</t>
+          <t xml:space="preserve">Übliche Fördersumme</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Typische oder maximale Förderhöhe laut Richtlinien oder Förderhistorie – kurz, z. B. „1.000–5.000 €, max. 10.000 €“ (höchstens etwa 80 Zeichen; Erläuterungen in „Notizen“).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pro – warum passt das?</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Begründung: Satzungszweck, Förderschwerpunkt, Regionalbezug, frühere Förderungen.</t>
+          <t xml:space="preserve">Eigenanteil gefordert</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ob und wie viel Eigenanteil verlangt wird – kurz, z. B. „ja, mind. 20 %“ oder „nein“ (höchstens etwa 80 Zeichen; Erläuterungen in „Notizen“).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contra – Knackpunkte</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wo es haken kann und worauf der Antrag den Fokus legen sollte.</t>
+          <t xml:space="preserve">Pro – warum passt das?</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Begründung: Satzungszweck, Förderschwerpunkt, Regionalbezug, frühere Förderungen.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Einschätzung</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
+          <t xml:space="preserve">Contra – Knackpunkte</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wo es haken kann und worauf der Antrag den Fokus legen sollte.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quellen</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Links zu Satzung, Förderrichtlinien und weiteren Belegen – je Link eine eigene Zeile in der Zelle (Zeilenumbruch), nur die Adresse, keine Trennzeichen wie „;“.</t>
+          <t xml:space="preserve">Einschätzung</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wie wahrscheinlich eine Förderung ist – nur: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich. Auswahl: sehr wahrscheinlich · wahrscheinlich · unsicher · unwahrscheinlich · sehr unwahrscheinlich</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quellen</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Links zu Satzung, Förderrichtlinien und weiteren Belegen – je Link eine eigene Zeile in der Zelle (Zeilenumbruch), nur die Adresse, keine Trennzeichen wie „;“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Notizen</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Alles Weitere.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -1262,6 +1269,7 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -248,7 +248,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stichwort oder Fördertopf</t>
+          <t xml:space="preserve">Stichworte oder Fördertöpfe</t>
         </is>
       </c>
       <c r="B11" s="4"/>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -129,6 +129,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -369,11 +372,11 @@
       <c r="D16" s="7"/>
       <c r="E16" s="8"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="9"/>
+      <c r="I16" s="10"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="10"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
@@ -389,11 +392,11 @@
       <c r="D17" s="7"/>
       <c r="E17" s="8"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="9"/>
+      <c r="I17" s="10"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="10"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -409,11 +412,11 @@
       <c r="D18" s="7"/>
       <c r="E18" s="8"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="G18" s="9"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="9"/>
+      <c r="I18" s="10"/>
       <c r="J18" s="8"/>
-      <c r="K18" s="10"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
@@ -429,11 +432,11 @@
       <c r="D19" s="7"/>
       <c r="E19" s="8"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="G19" s="9"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="9"/>
+      <c r="I19" s="10"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="10"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
@@ -449,11 +452,11 @@
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="G20" s="9"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="9"/>
+      <c r="I20" s="10"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="10"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
@@ -469,11 +472,11 @@
       <c r="D21" s="7"/>
       <c r="E21" s="8"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="G21" s="9"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="9"/>
+      <c r="I21" s="10"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="10"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -489,11 +492,11 @@
       <c r="D22" s="7"/>
       <c r="E22" s="8"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="G22" s="9"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="9"/>
+      <c r="I22" s="10"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="10"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -509,11 +512,11 @@
       <c r="D23" s="7"/>
       <c r="E23" s="8"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="G23" s="9"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="9"/>
+      <c r="I23" s="10"/>
       <c r="J23" s="8"/>
-      <c r="K23" s="10"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
@@ -529,11 +532,11 @@
       <c r="D24" s="7"/>
       <c r="E24" s="8"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="G24" s="9"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="9"/>
+      <c r="I24" s="10"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="10"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -549,11 +552,11 @@
       <c r="D25" s="7"/>
       <c r="E25" s="8"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="G25" s="9"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="9"/>
+      <c r="I25" s="10"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="10"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
@@ -569,11 +572,11 @@
       <c r="D26" s="7"/>
       <c r="E26" s="8"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="G26" s="9"/>
       <c r="H26" s="7"/>
-      <c r="I26" s="9"/>
+      <c r="I26" s="10"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="10"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
@@ -589,11 +592,11 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="G27" s="9"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="9"/>
+      <c r="I27" s="10"/>
       <c r="J27" s="8"/>
-      <c r="K27" s="10"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
@@ -609,11 +612,11 @@
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+      <c r="G28" s="9"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="9"/>
+      <c r="I28" s="10"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="10"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
@@ -629,11 +632,11 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="G29" s="9"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="9"/>
+      <c r="I29" s="10"/>
       <c r="J29" s="8"/>
-      <c r="K29" s="10"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
@@ -649,11 +652,11 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="G30" s="9"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="9"/>
+      <c r="I30" s="10"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="10"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -669,11 +672,11 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="G31" s="9"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="9"/>
+      <c r="I31" s="10"/>
       <c r="J31" s="8"/>
-      <c r="K31" s="10"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
@@ -689,11 +692,11 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+      <c r="G32" s="9"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="9"/>
+      <c r="I32" s="10"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="10"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
@@ -709,11 +712,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="G33" s="9"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="9"/>
+      <c r="I33" s="10"/>
       <c r="J33" s="8"/>
-      <c r="K33" s="10"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
@@ -729,11 +732,11 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+      <c r="G34" s="9"/>
       <c r="H34" s="7"/>
-      <c r="I34" s="9"/>
+      <c r="I34" s="10"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="10"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
@@ -749,11 +752,11 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="G35" s="9"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="9"/>
+      <c r="I35" s="10"/>
       <c r="J35" s="8"/>
-      <c r="K35" s="10"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="8"/>
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
@@ -769,11 +772,11 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
+      <c r="G36" s="9"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="9"/>
+      <c r="I36" s="10"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="10"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="8"/>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
@@ -789,11 +792,11 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="G37" s="9"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="9"/>
+      <c r="I37" s="10"/>
       <c r="J37" s="8"/>
-      <c r="K37" s="10"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
@@ -809,11 +812,11 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="G38" s="9"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="9"/>
+      <c r="I38" s="10"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="10"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
@@ -829,11 +832,11 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="G39" s="9"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="9"/>
+      <c r="I39" s="10"/>
       <c r="J39" s="8"/>
-      <c r="K39" s="10"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
@@ -849,11 +852,11 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="G40" s="9"/>
       <c r="H40" s="7"/>
-      <c r="I40" s="9"/>
+      <c r="I40" s="10"/>
       <c r="J40" s="8"/>
-      <c r="K40" s="10"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
       <c r="N40" s="8"/>
@@ -908,7 +911,7 @@
       </c>
     </row>
     <row r="2" ht="49" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Diese Datei ist die Vorlage für den Förderplan eines Bedarfs aus der Bedarfsliste (Fundraising, Malteser Hilfsdienst e. V., Diözese Paderborn). Sie wird von Hand oder von Copilot ausgefüllt und danach in der Bedarfsliste über „Excel übernehmen“ eingelesen. Der Bedarf mit Summe und noch offenem Betrag steht oben im Blatt „Förderplan“.</t>
         </is>
@@ -916,28 +919,28 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Auftrag</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Finde Förderer, die zu diesem Bedarf passen: Stiftungen, Sparkassen und Volksbanken, Unternehmen, Soziallotterien sowie öffentliche und kirchliche Förderprogramme. Förderer mit Bezug zum Erzbistum Paderborn und zu NRW zuerst, danach bundesweit.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Recherchiere im Web und prüfe jeden Förderer auf seinen eigenen Seiten: Satzungszweck, Förderrichtlinien, Antragsfristen, übliche Förderhöhe, geforderter Eigenanteil und Antragsweg. Trage als Quellen nur Links ein, die du dabei tatsächlich geöffnet hast. Wenn du nicht im Web suchen kannst, brich ab und sag es mir.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Förderer, die im Blatt „Förderplan“ schon stehen, nicht doppelt anlegen. Steht dort „zugesagt“ oder „abgelehnt“, die Zeile nicht ändern; sonst nur leere Zellen ergänzen.</t>
         </is>
@@ -945,14 +948,14 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Umfang</t>
         </is>
       </c>
     </row>
     <row r="10" ht="49" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">5 bis 8 Förderer, sortiert nach Erfolgsaussicht. Die erwartete Summe je Förderer realistisch aus Förderhistorie, Richtlinien oder üblicher Förderhöhe ableiten; geht das nicht, die Zelle leer lassen. Nicht auf eine Gesamtsumme hinrechnen. Lieber weniger Förderer mit Beleg als viele unsichere.</t>
         </is>
@@ -960,63 +963,63 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Regeln</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Je Förderer genau eine Zeile im Blatt „Förderplan“, ab der Zeile unter den Überschriften.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Spaltenüberschriften, Blattnamen und die Angaben oben (Bedarf, Kennung) nicht ändern.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Datum immer als TT.MM.JJJJ, Beträge nur als Zahl in Euro (ohne Text).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Art, Antragsweg und Einschätzung aus der Auswahlliste der Zelle wählen.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Kontakte: bis zu drei Personen, je Person eine Zeile in der Zelle „Name; Funktion; E-Mail; Telefon“.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Kurze Felder kurz halten: „Übliche Fördersumme“ und „Eigenanteil gefordert“ höchstens etwa 80 Zeichen – Erläuterungen gehören in „Notizen“.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Quellen: je Link eine eigene Zeile in der Zelle, nur die Adresse.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">• Unsicheres als solches kennzeichnen (z. B. „laut Website 2025, nicht bestätigt“). Nichts erfinden: lieber eine Zelle leer lassen.</t>
         </is>
@@ -1036,7 +1039,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Förderer</t>
         </is>
@@ -1048,7 +1051,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Stand in der Bedarfsliste</t>
         </is>
@@ -1060,7 +1063,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Art</t>
         </is>
@@ -1072,7 +1075,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Antragsweg</t>
         </is>
@@ -1084,7 +1087,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Kontakte</t>
         </is>
@@ -1096,7 +1099,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">E-Mail</t>
         </is>
@@ -1108,7 +1111,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Telefon</t>
         </is>
@@ -1120,7 +1123,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Website oder Portal-Link</t>
         </is>
@@ -1132,7 +1135,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Antragsfrist</t>
         </is>
@@ -1144,7 +1147,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Weitere Fristen und Termine</t>
         </is>
@@ -1156,7 +1159,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Erwartete Summe (€)</t>
         </is>
@@ -1168,7 +1171,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Übliche Fördersumme</t>
         </is>
@@ -1180,7 +1183,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Eigenanteil gefordert</t>
         </is>
@@ -1192,7 +1195,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Pro – warum passt das?</t>
         </is>
@@ -1204,7 +1207,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Contra – Knackpunkte</t>
         </is>
@@ -1216,7 +1219,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Einschätzung</t>
         </is>
@@ -1228,7 +1231,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Quellen</t>
         </is>
@@ -1240,7 +1243,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Notizen</t>
         </is>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -175,6 +175,7 @@
     <col min="16" max="16" width="22" customWidth="1"/>
     <col min="17" max="17" width="36" customWidth="1"/>
     <col min="18" max="18" width="30" customWidth="1"/>
+    <col min="19" max="19" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -362,6 +363,11 @@
       <c r="R15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Notizen</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ausführliche Recherche (Datei)</t>
         </is>
       </c>
     </row>
@@ -384,6 +390,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
+      <c r="S16" s="7"/>
     </row>
     <row r="17">
       <c r="A17" s="7"/>
@@ -404,6 +411,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
+      <c r="S17" s="7"/>
     </row>
     <row r="18">
       <c r="A18" s="7"/>
@@ -424,6 +432,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
+      <c r="S18" s="7"/>
     </row>
     <row r="19">
       <c r="A19" s="7"/>
@@ -444,6 +453,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
+      <c r="S19" s="7"/>
     </row>
     <row r="20">
       <c r="A20" s="7"/>
@@ -464,6 +474,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
+      <c r="S20" s="7"/>
     </row>
     <row r="21">
       <c r="A21" s="7"/>
@@ -484,6 +495,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
+      <c r="S21" s="7"/>
     </row>
     <row r="22">
       <c r="A22" s="7"/>
@@ -504,6 +516,7 @@
       <c r="P22" s="7"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
+      <c r="S22" s="7"/>
     </row>
     <row r="23">
       <c r="A23" s="7"/>
@@ -524,6 +537,7 @@
       <c r="P23" s="7"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
+      <c r="S23" s="7"/>
     </row>
     <row r="24">
       <c r="A24" s="7"/>
@@ -544,6 +558,7 @@
       <c r="P24" s="7"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
+      <c r="S24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="7"/>
@@ -564,6 +579,7 @@
       <c r="P25" s="7"/>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
+      <c r="S25" s="7"/>
     </row>
     <row r="26">
       <c r="A26" s="7"/>
@@ -584,6 +600,7 @@
       <c r="P26" s="7"/>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
+      <c r="S26" s="7"/>
     </row>
     <row r="27">
       <c r="A27" s="7"/>
@@ -604,6 +621,7 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
+      <c r="S27" s="7"/>
     </row>
     <row r="28">
       <c r="A28" s="7"/>
@@ -624,6 +642,7 @@
       <c r="P28" s="7"/>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
+      <c r="S28" s="7"/>
     </row>
     <row r="29">
       <c r="A29" s="7"/>
@@ -644,6 +663,7 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
+      <c r="S29" s="7"/>
     </row>
     <row r="30">
       <c r="A30" s="7"/>
@@ -664,6 +684,7 @@
       <c r="P30" s="7"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
+      <c r="S30" s="7"/>
     </row>
     <row r="31">
       <c r="A31" s="7"/>
@@ -684,6 +705,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
+      <c r="S31" s="7"/>
     </row>
     <row r="32">
       <c r="A32" s="7"/>
@@ -704,6 +726,7 @@
       <c r="P32" s="7"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
+      <c r="S32" s="7"/>
     </row>
     <row r="33">
       <c r="A33" s="7"/>
@@ -724,6 +747,7 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
+      <c r="S33" s="7"/>
     </row>
     <row r="34">
       <c r="A34" s="7"/>
@@ -744,6 +768,7 @@
       <c r="P34" s="7"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
+      <c r="S34" s="7"/>
     </row>
     <row r="35">
       <c r="A35" s="7"/>
@@ -764,6 +789,7 @@
       <c r="P35" s="7"/>
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
+      <c r="S35" s="7"/>
     </row>
     <row r="36">
       <c r="A36" s="7"/>
@@ -784,6 +810,7 @@
       <c r="P36" s="7"/>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
+      <c r="S36" s="7"/>
     </row>
     <row r="37">
       <c r="A37" s="7"/>
@@ -804,6 +831,7 @@
       <c r="P37" s="7"/>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
+      <c r="S37" s="7"/>
     </row>
     <row r="38">
       <c r="A38" s="7"/>
@@ -824,6 +852,7 @@
       <c r="P38" s="7"/>
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
+      <c r="S38" s="7"/>
     </row>
     <row r="39">
       <c r="A39" s="7"/>
@@ -844,6 +873,7 @@
       <c r="P39" s="7"/>
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
+      <c r="S39" s="7"/>
     </row>
     <row r="40">
       <c r="A40" s="7"/>
@@ -864,11 +894,12 @@
       <c r="P40" s="7"/>
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
+      <c r="S40" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
@@ -1254,6 +1285,18 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ausführliche Recherche (Datei)</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name der Word-Datei mit der ausführlichen Förderrecherche zu diesem Förderer (im Ordner des Bedarfs), z. B. „Förderrecherche – Sparkasse Paderborn.docx“.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A1:B1"/>

--- a/bedarfsliste-app/Foerderplan_Vorlage.xlsx
+++ b/bedarfsliste-app/Foerderplan_Vorlage.xlsx
@@ -956,10 +956,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="49" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Finde Förderer, die zu diesem Bedarf passen: Stiftungen, Sparkassen und Volksbanken, Unternehmen, Soziallotterien sowie öffentliche und kirchliche Förderprogramme. Förderer mit Bezug zum Erzbistum Paderborn und zu NRW zuerst, danach bundesweit.</t>
+          <t xml:space="preserve">1. Finde Förderer, die zu diesem Bedarf passen: Stiftungen, Sparkassen und Volksbanken, Unternehmen, Soziallotterien sowie öffentliche und kirchliche Förderprogramme. Förderer mit Bezug zum ganzen Gebiet des Erzbistums Paderborn (z. B. Paderborn, Dortmund, Hagen, Siegen, Höxter) und zu NRW zuerst, danach bundesweit.</t>
         </is>
       </c>
     </row>
